--- a/data/reports/report-2026-07-30.xlsx
+++ b/data/reports/report-2026-07-30.xlsx
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -675,7 +675,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>ただし全店の広告効率が3週連続で低下している。下の「ポートフォリオ警告」で判断が必要</t>
+          <t>ルール改定（P-1）を反映済み。改定により本日からP-1が発動中</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -685,369 +685,374 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>全店MER 2.81→2.80→2.71→2.38。直近週は−11.9%</t>
+          <t>全店MER 2.81→2.80→2.71→2.38。単週−11.9%が新条件②に該当</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>⚠️ 要判断</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+          <t>✅ 実装完了</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>害虫ブロッカーの増分MERが昨日から反転した。ただし本日は判定日ではないため操作しない</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>85,000円 据置</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>窓が1日伸びて 曜日+1.56→−0.00・全店+3.12→+2.24。7/29(水)がP2に入ったため。8/1の判定基準を下で再宣言</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>⚠️ 8/1に判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>■ ポートフォリオ警告（本日いちばん重要）</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="n"/>
+      <c r="C9" s="3" t="n"/>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="3" t="n"/>
+      <c r="F9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>実測</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>評価</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>全店MER（7日窓）</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>7/02-08 2.808 → 7/09-15 2.797（−0.4%）→ 7/16-22 2.706（−3.3%）→ 7/23-29 2.383（−11.9%）</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>4週連続で低下・直近が最大</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>W1(7/16-22)→W2(7/23-29)</t>
+          <t>全店MER（7日窓）</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>売上 9,717,712 → 9,465,870（−2.6%）／広告費 3,591,644 → 3,972,458（+10.6%）</t>
+          <t>7/02-08 2.808 → 7/09-15 2.797（−0.4%）→ 7/16-22 2.706（−3.3%）→ 7/23-29 2.383（−11.9%）</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>広告費を10.6%増やして売上は2.6%減った</t>
+          <t>4週連続で低下・直近が最大</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>同曜日どうしの比較</t>
+          <t>W1(7/16-22)→W2(7/23-29)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>木+3.1%／金−12.4%／土−5.7%／日+5.3%／月−24.4%／火−10.6%／水−32.4%</t>
+          <t>売上 9,717,712 → 9,465,870（−2.6%）／広告費 3,591,644 → 3,972,458（+10.6%）</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>曜日のせいではない。7日中5日が悪化</t>
+          <t>広告費を10.6%増やして売上は2.6%減った</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>MER低下の内訳（−0.521）</t>
+          <t>同曜日どうしの比較</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>4WAY −0.253／卓上冷感クーラー −0.092／完全遮光UV日傘 −0.070／害虫ブロッカー −0.051／5WAY −0.047</t>
+          <t>木+3.1%／金−12.4%／土−5.7%／日+5.3%／月−24.4%／火−10.6%／水−32.4%</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>上位5商品で98%を説明。5商品とも「予算を増やした商品」</t>
+          <t>曜日のせいではない。7日中5日が悪化</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>同5商品の予算増</t>
+          <t>MER低下の内訳（−0.521）</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>合計 +404,322円/週</t>
+          <t>4WAY −0.253／卓上冷感クーラー −0.092／完全遮光UV日傘 −0.070／害虫ブロッカー −0.051／5WAY −0.047</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>増やした分だけ効率が落ちている＝収穫逓減の限界を越えている</t>
+          <t>上位5商品で98%を説明。5商品とも「予算を増やした商品」</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>改善した商品</t>
+          <t>同5商品の予算増</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>瞬間冷感ポンチョ +0.038／ムダ毛シェーバー +0.028／UV歯ブラシ +0.018／接触冷感UVパーカー +0.010</t>
+          <t>合計 +404,322円/週</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>値上げ・複製リセット・予算復元が効いている</t>
+          <t>増やした分だけ効率が落ちている＝収穫逓減の限界を越えている</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>改善した商品</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>瞬間冷感ポンチョ +0.038／ムダ毛シェーバー +0.028／UV歯ブラシ +0.018／接触冷感UVパーカー +0.010</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>値上げ・複製リセット・予算復元が効いている</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>P-1ガードの状態</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>未発動（発動条件は「2週連続−5%以上」。直近は−3.3%→−11.9%で連続していない）</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>⚠️ ルールの穴。下で改定を提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>【改定後】発動中。新条件②「単週で−8%以上」に該当（−11.9%）</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>✅ 未測定のままの増額を禁止中</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>■ 本日の判定（宣言済みの基準に当てはめただけ）</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="3" t="n"/>
-      <c r="F18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>商品</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>宣言していた基準</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>実測</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>UV歯ブラシ除菌器</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>広告A-コピーのCPA &lt; 5,000円（購入10件未満なら証拠不足で延期）</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>A-コピー 消化53,819円／購入12件／CPA 4,485円（Bは14,594円/3件/CPA4,865円）</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>✅ 合格 → 10,000円で維持。7日利益+37,055円・余裕+0.86</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>■ 完了確認</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n"/>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>根拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>4WAY 予備CR追加</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>✅ 完了（7/27から3日越し）</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>7/29に広告Bが配信開始。消化42,739円・CTR2.90%・購入11件。単一CRの広告セットはゼロになった</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>ナノガラス脱毛パッド +12%増額</t>
+          <t>4WAY 予備CR追加</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>✅ 完了</t>
+          <t>✅ 完了（7/27から3日越し）</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>広告セット「ナノガラス脱毛パッド２」daily_budget=630（¥63,000）をMetaで確認。キャンペーン計76,000円</t>
+          <t>7/29に広告Bが配信開始。消化42,739円・CTR2.90%・購入11件。単一CRの広告セットはゼロになった</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>害虫ブロッカーのCVR急落（7/29に警戒）</t>
+          <t>ナノガラス脱毛パッド +12%増額</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>✅ 誤警報だった</t>
+          <t>✅ 完了</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>7/29の15時時点では1.24%だったが終日では2.48%。日中のCVRは構造的に低く出る。2%割れの連続条件は成立せず</t>
+          <t>広告セット「ナノガラス脱毛パッド２」daily_budget=630（¥63,000）をMetaで確認。キャンペーン計76,000円</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
+          <t>害虫ブロッカーのCVR急落（7/29に警戒）</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>✅ 誤警報だった</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>7/29の15時時点では1.24%だったが終日では2.48%。日中のCVRは構造的に低く出る。2%割れの連続条件は成立せず</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>湯上がりガーゼワンピース 7/26停止</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>✅ 停止は正解</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>減額分の増分MER 曜日+1.03／全店+1.03＜目標3.29。削った分は稼いでいなかった</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>■ 次の判定日（基準は宣言済み）</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n"/>
-      <c r="F29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>商品</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>合格基準</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>現時点の実測（参考・判定は当日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>7/31</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>5WAY腰掛けファン</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>7/28の増額分（13,000→16,250）の増分MER ≥ 分岐1.66</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>曜日+8.55／全店+9.94（Δ+3,527円/日）→ 両手法とも目標3.94超。合格見込みが高い</t>
         </is>
       </c>
     </row>
@@ -1059,17 +1064,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>4WAY</t>
+          <t>5WAY腰掛けファン</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>7/28の減額分の増分MER &lt; 目標3.48なら減額は正解＝85,000で維持</t>
+          <t>7/28の増額分（13,000→16,250）の増分MER ≥ 分岐1.66</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>曜日−0.07／全店−2.24（Δ−5,901円/日）→ 減額は正解の方向</t>
+          <t>曜日+8.55／全店+9.94（Δ+3,527円/日）→ 両手法とも目標3.94超。合格見込みが高い</t>
         </is>
       </c>
     </row>
@@ -1081,17 +1086,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>完全遮光・UV日傘</t>
+          <t>4WAY</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>同上（目標2.64）</t>
+          <t>7/28の減額分の増分MER &lt; 目標3.48なら減額は正解＝85,000で維持</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>曜日+0.60／全店+0.20 → 減額は正解の方向</t>
+          <t>曜日−0.07／全店−2.24（Δ−5,901円/日）→ 減額は正解の方向</t>
         </is>
       </c>
     </row>
@@ -1103,17 +1108,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>卓上冷感クーラー</t>
+          <t>完全遮光・UV日傘</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>同上（目標3.28）</t>
+          <t>同上（目標2.64）</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>曜日+1.14／全店+0.65 → 減額は正解の方向</t>
+          <t>曜日+0.60／全店+0.20 → 減額は正解の方向</t>
         </is>
       </c>
     </row>
@@ -1125,17 +1130,17 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>接触冷感UVパーカー</t>
+          <t>卓上冷感クーラー</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>34,000へ戻した後の7日MER ≥ 3.00</t>
+          <t>同上（目標3.28）</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>2.88（あと0.12）</t>
+          <t>曜日+1.14／全店+0.65 → 減額は正解の方向</t>
         </is>
       </c>
     </row>
@@ -1147,39 +1152,39 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>秋物の選定</t>
+          <t>接触冷感UVパーカー</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>ジェットウォッシャー／姿勢サポートベルト／癒しの指圧マット</t>
+          <t>34,000へ戻した後の7日MER ≥ 3.00</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.88（あと0.12）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>8/1</t>
+          <t>7/31</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>害虫ブロッカー</t>
+          <t>秋物の選定</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>増分MERの2手法が同ゾーンに収束し下限 ≥ 目標2.43なら+20%</t>
+          <t>ジェットウォッシャー／姿勢サポートベルト／癒しの指圧マット</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>曜日−0.00／全店+2.24＝依然として割れている</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1191,17 +1196,17 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>瞬間冷感ポンチョ</t>
+          <t>害虫ブロッカー【基準を再宣言】</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>MER2.91 ≥ 目標2.60・消化105%で増額候補。+25%（13,000→16,250）で測定を兼ねる</t>
+          <t>増分MERの下限（2手法の悪い方）で機械的に判定する。①下限 ≥ 目標2.43 → +20%（85,000→102,000）／②分岐1.31 ≤ 下限 &lt; 目標 → 85,000で据置 ／③下限 &lt; 分岐1.31 → 73,000へ戻す。ただし7/27のCR投入がP2に混入し予算増とCR投入が分離できないため、P2を7/30以降（CR投入から3日以降）に限定して再計算した値で判定する</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>曜日−0.00／全店+2.24。P1→P2で広告費+10,222円/日に対し売上+398円/日＝追加分の売上がほぼ検出できていない。本日は判定日ではないため操作しない（戻すと学習が2度目のリセットになるリスクもある）</t>
         </is>
       </c>
     </row>
@@ -1213,168 +1218,253 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>手数料の月次再計測</t>
+          <t>瞬間冷感ポンチョ【基準を変更】</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>直近100注文の決済ゲートウェイ構成比×料率でブレンド率を更新（現行3.49%）</t>
+          <t>P-1発動中は未測定の増額を禁止するため、8/1は13,000円で据置。次に予算を動かすときに±25%以上動かして増分MERを測定可能にする</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MER2.91 ≥ 目標2.60・消化105%で本来は増額候補だが、増分MERが未測定</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>8/2</t>
+          <t>8/1</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>ナノガラス脱毛パッド</t>
+          <t>手数料の月次再計測</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>7/29の増額分（68,000→76,000）の増分MER ≥ 分岐1.24</t>
+          <t>直近100注文の決済ゲートウェイ構成比×料率でブレンド率を更新（現行3.49%）</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>P2が1日のみで測定不可。8/2に判定</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>8/3</t>
+          <t>8/2</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>卓上／害虫／ムダ毛</t>
+          <t>ナノガラス脱毛パッド</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>卓上: LP改修後CVR ≥ 2.5%（現1.82%）／害虫: 追加CRのCTR ≥ 3.0%（現2.79%）／ムダ毛: 7日販売数 ≥ 35個（現47個）</t>
+          <t>7/29の増額分（68,000→76,000）の増分MER ≥ 分岐1.24</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>P2が1日のみで測定不可。8/2に判定</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>8/4</t>
+          <t>8/3</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>壁掛けディスペンサー</t>
+          <t>卓上／害虫／ムダ毛</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>LP改修後の7日CVR ≥ 2.5%（現1.95%）</t>
+          <t>卓上: LP改修後CVR ≥ 2.5%（現1.82%）／害虫: 追加CRのCTR ≥ 3.0%（現2.79%）／ムダ毛: 7日販売数 ≥ 35個（現47個）</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>未達なら停止し6,000円を転用</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
+          <t>8/4</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>壁掛けディスペンサー</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>LP改修後の7日CVR ≥ 2.5%（現1.95%）</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>未達なら停止し6,000円を転用</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
           <t>8/5</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>アームカバー／携帯シェーバー／サングラス</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>余裕 ≥ +0.8（現+0.71）／7日MER ≥ 1.90（現1.71）／LP改修後CVR ≥ 3.2%（現2.70%）</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>■ ルール改定の提案（実施はユーザー判断）</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n"/>
-      <c r="C45" s="3" t="n"/>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
-      <c r="F45" s="3" t="n"/>
-    </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>現行</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>問題</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>提案</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>■ ルール改定（ユーザー承認・本日 decision_flow.py に実装済み）</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n"/>
+      <c r="C46" s="3" t="n"/>
+      <c r="D46" s="3" t="n"/>
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>P-1: 週次MERが2週連続で−5%以上悪化したら全商品の増額を凍結</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>直近が−3.3%→−11.9%。1週で−11.9%という2週分より大きい悪化を取りこぼす</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>P-1に「単週で−8%以上」をOR条件として追加する</t>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>改定</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>本日以降の効果</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>凍結の対象は全商品</t>
+          <t>P-1の発動条件に②を追加</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>5WAY腰掛けファンの増分MERは曜日+8.55／全店+9.94で、凍結すると明確に儲かる増額を止めてしまう</t>
+          <t>①2週連続で−5%以上 **または ②単週で−8%以上**</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>全面凍結ではなく「増額には実測の増分MERが目標超えであることを必須にする」に変える（未測定なら増額しない）</t>
+          <t>直近が−11.9%なので②で発動中。実装は calc*.py の P1_A/P1_B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>一律凍結をやめ「未測定の増額禁止」に変更</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>増額には実測の増分MERが目標MER以上であることを必須にする。未測定なら据置（次に動かすときに±25%以上動かして測定可能にする）</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>5WAY腰掛けファン（増分+9.25）は増額を許可／瞬間冷感ポンチョ（未測定）は8/1に増額せず据置に変わった</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>【付随して発覚した不具合を修正】S2cを追加</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>平均MERが目標をわずかに下回る商品は S2a→S2b へ逸れて S5 に到達せず、増分MERが目標を大きく超えていても増額されなかった。「平均MERが目標未達でも 増分MER ≥ 目標 かつ 消化率 ≥ 95% なら増額する」を追加</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>5WAY腰掛けファン（平均3.89 &lt; 目標3.94 だが増分+9.25）が「維持」から「+25%増額」に変わった。承認いただいた改定を機能させるために必要な修正だったため同時に入れた</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>■ 追加で提案したいルール（P-2・実施はユーザー判断）</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n"/>
+      <c r="C52" s="3" t="n"/>
+      <c r="D52" s="3" t="n"/>
+      <c r="E52" s="3" t="n"/>
+      <c r="F52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>提案</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>根拠</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>効果</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>未測定の予算変更は同時に1商品までにする</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>今週の悪化はW1→W2で4WAY・卓上・完全遮光・害虫・5WAYの5商品を同時に増額したことで起きた（合計+404,322円/週）。さらに同時変更はV8（全店コントロールから同時期に変更した他商品を除く）に違反しており、増分MERの全店補正が互いに汚染される。害虫の2手法が−0.00と+2.24に割れているのはこれが原因</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>①ポートフォリオの下振れが1/5になる ②増分MERがきれいに測れる ③どの変更が効いたか特定できる</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4525,7 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>ネックマッサージャー</t>
+          <t>癒しの指圧マット</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
@@ -4480,7 +4570,7 @@
       </c>
       <c r="R24" s="8" t="inlineStr"/>
       <c r="S24" s="10" t="n">
-        <v>6946</v>
+        <v>4332</v>
       </c>
       <c r="T24" s="8" t="inlineStr"/>
       <c r="U24" s="8" t="inlineStr"/>
@@ -4515,7 +4605,7 @@
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>姿勢サポートベルト</t>
+          <t>ナノバブルシャワーヘッド</t>
         </is>
       </c>
       <c r="B25" s="21" t="n">
@@ -4560,7 +4650,7 @@
       </c>
       <c r="R25" s="20" t="inlineStr"/>
       <c r="S25" s="21" t="n">
-        <v>4551</v>
+        <v>28350</v>
       </c>
       <c r="T25" s="20" t="inlineStr"/>
       <c r="U25" s="20" t="inlineStr"/>
@@ -4595,7 +4685,7 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>癒しの指圧マット</t>
+          <t>ネックマッサージャー</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
@@ -4640,7 +4730,7 @@
       </c>
       <c r="R26" s="8" t="inlineStr"/>
       <c r="S26" s="10" t="n">
-        <v>4332</v>
+        <v>6946</v>
       </c>
       <c r="T26" s="8" t="inlineStr"/>
       <c r="U26" s="8" t="inlineStr"/>
@@ -4675,7 +4765,7 @@
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>ナノバブルシャワーヘッド</t>
+          <t>リカバリーサンダル</t>
         </is>
       </c>
       <c r="B27" s="21" t="n">
@@ -4720,7 +4810,7 @@
       </c>
       <c r="R27" s="20" t="inlineStr"/>
       <c r="S27" s="21" t="n">
-        <v>28350</v>
+        <v>16026</v>
       </c>
       <c r="T27" s="20" t="inlineStr"/>
       <c r="U27" s="20" t="inlineStr"/>
@@ -4755,7 +4845,7 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>リカバリーサンダル</t>
+          <t>姿勢サポートベルト</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
@@ -4800,7 +4890,7 @@
       </c>
       <c r="R28" s="8" t="inlineStr"/>
       <c r="S28" s="10" t="n">
-        <v>16026</v>
+        <v>4551</v>
       </c>
       <c r="T28" s="8" t="inlineStr"/>
       <c r="U28" s="8" t="inlineStr"/>
@@ -4997,7 +5087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5038,12 +5128,12 @@
       </c>
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>【全体ガード】週次MER（7日窓）が2週連続で−5%以上悪化していないか？</t>
+          <t>【全体ガード】週次MER（7日窓）が **①2週連続で−5%以上 または ②単週で−8%以上** 悪化していないか？（2026-07-30ユーザー承認で②を追加）</t>
         </is>
       </c>
       <c r="C4" s="34" t="inlineStr">
         <is>
-          <t>悪化している→全商品の増額を凍結し、巻き戻し・秋物テスト・広告以外のレバーへ軸足を移す（個別最適の増額がポートフォリオ悪化を隠すのを防ぐ）。judge() に実装済み（P1凍結フラグ）。2026-07-29時点: 2.92→2.71→2.67→2.52（−7.4%／−1.3%／−5.4%）＝連続でないため未発動・監視継続</t>
+          <t>悪化している→**増額には「実測の増分MERが目標MER以上」であることを必須にする**（＝未測定のままの増額を禁止する）。全商品の増額を一律凍結はしない（2026-07-30ユーザー承認で変更。一律凍結は5WAY腰掛けファンのように増分MERが目標を大きく超える明確に儲かる増額まで止めてしまうため）。あわせて巻き戻し・秋物テスト・広告以外のレバーへ軸足を移す。judge() に実装済み（P1警戒フラグ）。2026-07-30時点: 2.808→2.797→2.706→**2.383**（−0.4%／−3.3%／**−11.9%**）＝②により**発動中**</t>
         </is>
       </c>
     </row>
@@ -5169,1415 +5259,1432 @@
     <row r="12">
       <c r="A12" s="32" t="inlineStr">
         <is>
-          <t>S2b</t>
+          <t>S2c</t>
         </is>
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>その予算を「目標MER超え×消化率95%以上」の商品に回した方が利益が大きいか？</t>
+          <t>【S2aの後・2026-07-30追加】平均MERは目標未達でも **実測の増分MER ≥ 目標MER かつ 消化率 ≥ 95%** か？</t>
         </is>
       </c>
       <c r="C12" s="34" t="inlineStr">
         <is>
-          <t>転用先の増収は**実測の増分MER**で評価する（平均MERで評価しない。平均MERは既存売上に支えられており、追加1円の成績ではない）。転用先の増分MERが実測されていない、または実測値が転用先の分岐MERを下回るなら『回しても増えない』＝転用しない。YES→停止して転用 ／ NO→維持し、CR・LP・価格で手当て</t>
+          <t>YES→+20〜30%増額。予算の増減は平均ではなく**限界（追加1円の成績）**で決めるという原則の徹底。これを入れないと平均MERが目標をわずかに下回る商品がS2a→S2bへ逸れてS5に到達せず、増分MERが目標を大きく超えていても増額されない（2026-07-30に5WAY腰掛けファンで発覚: 平均MER3.89 &lt; 目標3.94 だが増分MERは曜日+8.55／全店+9.94）／NO→S2bへ</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="32" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S2b</t>
         </is>
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>直近2日の消化率 ≥ 95% か？</t>
+          <t>その予算を「目標MER超え×消化率95%以上」の商品に回した方が利益が大きいか？</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>NO→枠が余っている。増額しても消化できない→据置 ／ YES→S4へ（枠で止まっている）</t>
+          <t>転用先の増収は**実測の増分MER**で評価する（平均MERで評価しない。平均MERは既存売上に支えられており、追加1円の成績ではない）。転用先の増分MERが実測されていない、または実測値が転用先の分岐MERを下回るなら『回しても増えない』＝転用しない。YES→停止して転用 ／ NO→維持し、CR・LP・価格で手当て</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="32" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>増分MERを測定済みか？</t>
+          <t>直近2日の消化率 ≥ 95% か？</t>
         </is>
       </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>未測定→+25%増額（機会を取りにいくと同時に測定可能にする） ／ 測定済→S5へ ／ **測定済だが曜日補正と全店補正が『分岐〜目標』の帯をまたいで割れている場合は増額しない**（据置して次の判定日に持ち越す。片方だけを採用しない。2026-07-29 害虫ブロッカーが該当: 曜日+1.80／全店+3.59）</t>
+          <t>NO→枠が余っている。増額しても消化できない→据置 ／ YES→S4へ（枠で止まっている）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="32" t="inlineStr">
         <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>増分MERを測定済みか？</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>未測定→+25%増額（機会を取りにいくと同時に測定可能にする） ／ 測定済→S5へ ／ **測定済だが曜日補正と全店補正が『分岐〜目標』の帯をまたいで割れている場合は増額しない**（据置して次の判定日に持ち越す。片方だけを採用しない。2026-07-29 害虫ブロッカーが該当: 曜日+1.80／全店+3.59）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>増分MER と しきい値の比較</t>
         </is>
       </c>
-      <c r="C15" s="34" t="inlineStr">
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>≥目標MER→+20〜30%増額 ／ 分岐≤増分&lt;目標→据置（利益は増えるが利益率が下がる） ／ &lt;分岐→元の予算に戻す</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>【D:原因分解】減額の前に必ず実施。週次のCTR/CVR/CPM/頻度を前週と比べる</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t>CTRの2週間累積変化が −15%以下か？（連続低下だけでは判定しない）</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="inlineStr">
-        <is>
-          <t>→素材疲弊。**その広告セットに新CRを追加**する。既存CRは止めない（同一セット内はMetaが自動配分するため）。予算は据置し7日後に再判定</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="32" t="inlineStr">
         <is>
-          <t>D1b</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B19" s="33" t="inlineStr">
         <is>
-          <t>その広告セットで配信されているCRが1本だけか？</t>
+          <t>CTRの2週間累積変化が −15%以下か？（連続低下だけでは判定しない）</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>→疲弊が起きたときに受け皿がない。CTR劣化がなくても、日予算の大きいセットから順に**予備CRを1本足しておく**（予算・既存CRは触らない）</t>
+          <t>→素材疲弊。**その広告セットに新CRを追加**する。既存CRは止めない（同一セット内はMetaが自動配分するため）。予算は据置し7日後に再判定</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="32" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D1b</t>
         </is>
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>頻度 &gt; 2.5 か？</t>
+          <t>その広告セットで配信されているCRが1本だけか？</t>
         </is>
       </c>
       <c r="C20" s="34" t="inlineStr">
         <is>
-          <t>→疲弊確定。①オーディエンス拡大（類似%↑/全開放）②新CR③配信面を広げる。**予算は据置**</t>
+          <t>→疲弊が起きたときに受け皿がない。CTR劣化がなくても、日予算の大きいセットから順に**予備CRを1本足しておく**（予算・既存CRは触らない）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="32" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
-          <t>CVR（購入÷アウトバウンドクリック）が前週比 −15%以下か？</t>
+          <t>頻度 &gt; 2.5 か？</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>→LP/オファーの問題。①LP改善（FV・レビュー・配送日数）②価格/送料訴求③優先配送の見せ方。**予算は据置**</t>
+          <t>→疲弊確定。①オーディエンス拡大（類似%↑/全開放）②新CR③配信面を広げる。**予算は据置**</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="32" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B22" s="33" t="inlineStr">
         <is>
-          <t>CPMが前週比 +15%以上か？</t>
+          <t>CVR（購入÷アウトバウンドクリック）が前週比 −15%以下か？</t>
         </is>
       </c>
       <c r="C22" s="34" t="inlineStr">
         <is>
-          <t>→①全開放(Advantage+)②配信面の偏り確認③訴求替えCR④値上げで高CPMを回収できる経済性にする</t>
+          <t>→LP/オファーの問題。①LP改善（FV・レビュー・配送日数）②価格/送料訴求③優先配送の見せ方。**予算は据置**</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="32" t="inlineStr">
         <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B23" s="33" t="inlineStr">
+        <is>
+          <t>CPMが前週比 +15%以上か？</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>→①全開放(Advantage+)②配信面の偏り確認③訴求替えCR④値上げで高CPMを回収できる経済性にする</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
           <t>D5</t>
         </is>
       </c>
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>CTR・CVR・CPMすべて横ばいでCPAだけ悪化か？</t>
         </is>
       </c>
-      <c r="C23" s="34" t="inlineStr">
+      <c r="C24" s="34" t="inlineStr">
         <is>
           <t>→需要減衰。CRでは直らない。**ここで初めて減額**。季節終盤なら段階縮小</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t>【CRフロー】予算フローとは独立に判定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="32" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>悪化の先行指標が出ているか？</t>
-        </is>
-      </c>
-      <c r="C26" s="34" t="inlineStr">
-        <is>
-          <t>頻度&gt;2.5 ／ CTR2週連続低下 ／ 余裕3日連続縮小 ／ 7日利益2週連続減。NO→健全な商品はCRも触らない</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="32" t="inlineStr">
         <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>悪化の先行指標が出ているか？</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>頻度&gt;2.5 ／ CTR2週連続低下 ／ 余裕3日連続縮小 ／ 7日利益2週連続減。NO→健全な商品はCRも触らない</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
           <t>C2</t>
         </is>
       </c>
-      <c r="B27" s="33" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>新素材はあるか？</t>
         </is>
       </c>
-      <c r="C27" s="34" t="inlineStr">
+      <c r="C28" s="34" t="inlineStr">
         <is>
           <t>YES→既存広告セットに追加し判定日を+7日リセット ／ NO→複製リセット・価格・オーディエンス替えで代替</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="31" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>【増分MERの算出】Δ売上(曜日補正後) ÷ Δ広告費</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>V1</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>|Δ広告費| ≥ 3,000円/日 か？</t>
-        </is>
-      </c>
-      <c r="C30" s="34" t="inlineStr">
-        <is>
-          <t>未満は分母が小さく値が発散するため測定しない</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="32" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B31" s="33" t="inlineStr">
         <is>
-          <t>予算を意図的に変えたか？</t>
+          <t>|Δ広告費| ≥ 3,000円/日 か？</t>
         </is>
       </c>
       <c r="C31" s="34" t="inlineStr">
         <is>
-          <t>変えていない場合、消化の増減はMetaのペーシング。成績が悪い日に自動で絞る逆因果を含むため実験にならない</t>
+          <t>未満は分母が小さく値が発散するため測定しない</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="32" t="inlineStr">
         <is>
-          <t>V3</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>P1・P2とも予算変更日をまたいでいないか？</t>
+          <t>予算を意図的に変えたか？</t>
         </is>
       </c>
       <c r="C32" s="34" t="inlineStr">
         <is>
-          <t>またぐと変更前後が混ざり測定にならない</t>
+          <t>変えていない場合、消化の増減はMetaのペーシング。成績が悪い日に自動で絞る逆因果を含むため実験にならない</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="32" t="inlineStr">
         <is>
-          <t>V4</t>
+          <t>V3</t>
         </is>
       </c>
       <c r="B33" s="33" t="inlineStr">
         <is>
-          <t>曜日構成を補正したか？</t>
+          <t>P1・P2とも予算変更日をまたいでいないか？</t>
         </is>
       </c>
       <c r="C33" s="34" t="inlineStr">
         <is>
-          <t>P1とP2の曜日指数の平均比で後期間の売上を補正する。補正しないと結論が反転する</t>
+          <t>またぐと変更前後が混ざり測定にならない</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="32" t="inlineStr">
         <is>
-          <t>V5</t>
+          <t>V4</t>
         </is>
       </c>
       <c r="B34" s="33" t="inlineStr">
         <is>
-          <t>P1・P2の全日付が広告費データに存在するか？</t>
+          <t>曜日構成を補正したか？</t>
         </is>
       </c>
       <c r="C34" s="34" t="inlineStr">
         <is>
-          <t>**存在しない日はゼロ扱いになり増分が大きく歪む。必ずassertする**（2026-07-28: 7日窓のスライドでP1の7/20が欠落し、パーカーの増分を+2.4〜5.4→+0.93と誤計測。巻き戻し指示を誤発行した）</t>
+          <t>P1とP2の曜日指数の平均比で後期間の売上を補正する。補正しないと結論が反転する</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="32" t="inlineStr">
         <is>
-          <t>V6</t>
+          <t>V5</t>
         </is>
       </c>
       <c r="B35" s="33" t="inlineStr">
         <is>
-          <t>P1・P2に祝日が含まれていないか？</t>
+          <t>P1・P2の全日付が広告費データに存在するか？</t>
         </is>
       </c>
       <c r="C35" s="34" t="inlineStr">
         <is>
-          <t>祝日は曜日指数が通用しない（海の日の月曜は平常月曜の+37%）。P1から除外するか、やむを得ない場合は日曜指数を適用する</t>
+          <t>**存在しない日はゼロ扱いになり増分が大きく歪む。必ずassertする**（2026-07-28: 7日窓のスライドでP1の7/20が欠落し、パーカーの増分を+2.4〜5.4→+0.93と誤計測。巻き戻し指示を誤発行した）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="32" t="inlineStr">
         <is>
-          <t>V7</t>
+          <t>V6</t>
         </is>
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>増分MERが負の場合の読み方</t>
+          <t>P1・P2に祝日が含まれていないか？</t>
         </is>
       </c>
       <c r="C36" s="34" t="inlineStr">
         <is>
-          <t>広告が売上を消すことはないため、負値は文字通りには成立しない。予算増は好調期の直後に行われがちで平均回帰によりP1が上振れする（負に偏るバイアス）。**負値は「増額分の追加売上は検出されず＝実質ゼロ以下」と読む**。分岐割れの結論自体は頑健</t>
+          <t>祝日は曜日指数が通用しない（海の日の月曜は平常月曜の+37%）。P1から除外するか、やむを得ない場合は日曜指数を適用する</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="32" t="inlineStr">
         <is>
-          <t>V8</t>
+          <t>V7</t>
         </is>
       </c>
       <c r="B37" s="33" t="inlineStr">
         <is>
-          <t>全店コントロールから、同時期に予算・CR・価格を変更した他商品を除いているか？</t>
+          <t>増分MERが負の場合の読み方</t>
         </is>
       </c>
       <c r="C37" s="34" t="inlineStr">
         <is>
-          <t>除かないとコントロール自体が動き補正が汚染される</t>
+          <t>広告が売上を消すことはないため、負値は文字通りには成立しない。予算増は好調期の直後に行われがちで平均回帰によりP1が上振れする（負に偏るバイアス）。**負値は「増額分の追加売上は検出されず＝実質ゼロ以下」と読む**。分岐割れの結論自体は頑健</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="32" t="inlineStr">
         <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B38" s="33" t="inlineStr">
+        <is>
+          <t>全店コントロールから、同時期に予算・CR・価格を変更した他商品を除いているか？</t>
+        </is>
+      </c>
+      <c r="C38" s="34" t="inlineStr">
+        <is>
+          <t>除かないとコントロール自体が動き補正が汚染される</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="32" t="inlineStr">
+        <is>
           <t>V9</t>
         </is>
       </c>
-      <c r="B38" s="33" t="inlineStr">
+      <c r="B39" s="33" t="inlineStr">
         <is>
           <t>P1+P2の合計購入件数 ≥ 25件か？</t>
         </is>
       </c>
-      <c r="C38" s="34" t="inlineStr">
+      <c r="C39" s="34" t="inlineStr">
         <is>
           <t>未満は小標本ノイズで窓のスライドだけで結論が反転する（スリッパは20件で+0.7→+3.3に振れた）。測定不能として扱う。CPA基準の判定（UV歯ブラシ等）も購入10件未満なら証拠不足として延期</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>■ 本日の全商品トレース（どの分岐を通ってその結論になったか）</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>商品</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>日販</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>7日利益</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>MER</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>目標MER</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>分岐</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
         <is>
           <t>余裕</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>消化率</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>増分MER</t>
         </is>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr">
         <is>
           <t>判定日</t>
         </is>
       </c>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="K43" s="4" t="inlineStr">
         <is>
           <t>現予算</t>
         </is>
       </c>
-      <c r="L42" s="4" t="inlineStr">
+      <c r="L43" s="4" t="inlineStr">
         <is>
           <t>提案予算</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>結論</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
+      <c r="N43" s="4" t="inlineStr">
         <is>
           <t>通った分岐</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>4WAY 取り付けOK 小型瞬間冷却ハンディファン</t>
         </is>
       </c>
-      <c r="B43" s="35" t="n">
+      <c r="B44" s="35" t="n">
         <v>53.3</v>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C44" s="10" t="n">
         <v>499898</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D44" s="16" t="n">
         <v>2.81</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E44" s="16" t="n">
         <v>3.48</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F44" s="16" t="n">
         <v>1.57</v>
       </c>
-      <c r="G43" s="16" t="n">
+      <c r="G44" s="16" t="n">
         <v>1.24</v>
       </c>
-      <c r="H43" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="16" t="n">
+      <c r="H44" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="16" t="n">
         <v>-1.16</v>
       </c>
-      <c r="J43" s="8" t="inlineStr">
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>7/31</t>
         </is>
       </c>
-      <c r="K43" s="10" t="n">
+      <c r="K44" s="10" t="n">
         <v>85000</v>
       </c>
-      <c r="L43" s="10" t="n">
+      <c r="L44" s="10" t="n">
         <v>85000</v>
       </c>
-      <c r="M43" s="8" t="inlineStr">
+      <c r="M44" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/31）</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>害虫ブロッカー</t>
         </is>
       </c>
-      <c r="B44" s="37" t="n">
+      <c r="B45" s="37" t="n">
         <v>49.1</v>
       </c>
-      <c r="C44" s="21" t="n">
+      <c r="C45" s="21" t="n">
         <v>394639</v>
       </c>
-      <c r="D44" s="23" t="n">
+      <c r="D45" s="23" t="n">
         <v>2.25</v>
       </c>
-      <c r="E44" s="23" t="n">
+      <c r="E45" s="23" t="n">
         <v>2.43</v>
       </c>
-      <c r="F44" s="23" t="n">
+      <c r="F45" s="23" t="n">
         <v>1.31</v>
       </c>
-      <c r="G44" s="23" t="n">
+      <c r="G45" s="23" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="H44" s="38" t="n">
+      <c r="H45" s="38" t="n">
         <v>0.964</v>
       </c>
-      <c r="I44" s="20" t="inlineStr">
+      <c r="I45" s="20" t="inlineStr">
         <is>
           <t>割れ -0.00/2.24</t>
         </is>
       </c>
-      <c r="J44" s="20" t="inlineStr">
+      <c r="J45" s="20" t="inlineStr">
         <is>
           <t>8/1</t>
         </is>
       </c>
-      <c r="K44" s="21" t="n">
+      <c r="K45" s="21" t="n">
         <v>85000</v>
       </c>
-      <c r="L44" s="21" t="n">
+      <c r="L45" s="21" t="n">
         <v>85000</v>
       </c>
-      <c r="M44" s="20" t="inlineStr">
+      <c r="M45" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N44" s="24" t="inlineStr">
+      <c r="N45" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 8/1）</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
         <is>
           <t>形状記憶日傘</t>
         </is>
       </c>
-      <c r="B45" s="35" t="n">
+      <c r="B46" s="35" t="n">
         <v>36.1</v>
       </c>
-      <c r="C45" s="10" t="n">
+      <c r="C46" s="10" t="n">
         <v>487590</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D46" s="16" t="n">
         <v>3.02</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E46" s="16" t="n">
         <v>2.63</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="F46" s="16" t="n">
         <v>1.37</v>
       </c>
-      <c r="G45" s="16" t="n">
+      <c r="G46" s="16" t="n">
         <v>1.65</v>
       </c>
-      <c r="H45" s="36" t="n">
+      <c r="H46" s="36" t="n">
         <v>0.986</v>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J45" s="8" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>なし(健全)</t>
         </is>
       </c>
-      <c r="K45" s="10" t="n">
+      <c r="K46" s="10" t="n">
         <v>60000</v>
       </c>
-      <c r="L45" s="10" t="n">
+      <c r="L46" s="10" t="n">
         <v>60000</v>
       </c>
-      <c r="M45" s="8" t="inlineStr">
+      <c r="M46" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 なし(健全)）</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>ナノガラス脱毛パッド</t>
         </is>
       </c>
-      <c r="B46" s="37" t="n">
+      <c r="B47" s="37" t="n">
         <v>37.3</v>
       </c>
-      <c r="C46" s="21" t="n">
+      <c r="C47" s="21" t="n">
         <v>382372</v>
       </c>
-      <c r="D46" s="23" t="n">
+      <c r="D47" s="23" t="n">
         <v>2.31</v>
       </c>
-      <c r="E46" s="23" t="n">
+      <c r="E47" s="23" t="n">
         <v>2.18</v>
       </c>
-      <c r="F46" s="23" t="n">
+      <c r="F47" s="23" t="n">
         <v>1.24</v>
       </c>
-      <c r="G46" s="23" t="n">
+      <c r="G47" s="23" t="n">
         <v>1.07</v>
       </c>
-      <c r="H46" s="38" t="n">
+      <c r="H47" s="38" t="n">
         <v>0.998</v>
       </c>
-      <c r="I46" s="20" t="inlineStr">
+      <c r="I47" s="20" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J46" s="20" t="inlineStr">
+      <c r="J47" s="20" t="inlineStr">
         <is>
           <t>8/2</t>
         </is>
       </c>
-      <c r="K46" s="21" t="n">
+      <c r="K47" s="21" t="n">
         <v>76000</v>
       </c>
-      <c r="L46" s="21" t="n">
+      <c r="L47" s="21" t="n">
         <v>76000</v>
       </c>
-      <c r="M46" s="20" t="inlineStr">
+      <c r="M47" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N46" s="24" t="inlineStr">
+      <c r="N47" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 8/2）</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>接触冷感UVパーカー</t>
         </is>
       </c>
-      <c r="B47" s="35" t="n">
+      <c r="B48" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="C47" s="10" t="n">
+      <c r="C48" s="10" t="n">
         <v>186175</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D48" s="16" t="n">
         <v>2.88</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E48" s="16" t="n">
         <v>3.55</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F48" s="16" t="n">
         <v>1.58</v>
       </c>
-      <c r="G47" s="16" t="n">
+      <c r="G48" s="16" t="n">
         <v>1.3</v>
       </c>
-      <c r="H47" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="H48" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J48" s="8" t="inlineStr">
         <is>
           <t>7/31</t>
         </is>
       </c>
-      <c r="K47" s="10" t="n">
+      <c r="K48" s="10" t="n">
         <v>34000</v>
       </c>
-      <c r="L47" s="10" t="n">
+      <c r="L48" s="10" t="n">
         <v>34000</v>
       </c>
-      <c r="M47" s="8" t="inlineStr">
+      <c r="M48" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/31）</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>卓上冷感クーラー</t>
         </is>
       </c>
-      <c r="B48" s="37" t="n">
+      <c r="B49" s="37" t="n">
         <v>15.4</v>
       </c>
-      <c r="C48" s="21" t="n">
+      <c r="C49" s="21" t="n">
         <v>184568</v>
       </c>
-      <c r="D48" s="23" t="n">
+      <c r="D49" s="23" t="n">
         <v>2.78</v>
       </c>
-      <c r="E48" s="23" t="n">
+      <c r="E49" s="23" t="n">
         <v>3.28</v>
       </c>
-      <c r="F48" s="23" t="n">
+      <c r="F49" s="23" t="n">
         <v>1.53</v>
       </c>
-      <c r="G48" s="23" t="n">
+      <c r="G49" s="23" t="n">
         <v>1.25</v>
       </c>
-      <c r="H48" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="23" t="n">
+      <c r="H49" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="23" t="n">
         <v>0.9</v>
       </c>
-      <c r="J48" s="20" t="inlineStr">
+      <c r="J49" s="20" t="inlineStr">
         <is>
           <t>7/31</t>
         </is>
       </c>
-      <c r="K48" s="21" t="n">
+      <c r="K49" s="21" t="n">
         <v>30000</v>
       </c>
-      <c r="L48" s="21" t="n">
+      <c r="L49" s="21" t="n">
         <v>30000</v>
       </c>
-      <c r="M48" s="20" t="inlineStr">
+      <c r="M49" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N48" s="24" t="inlineStr">
+      <c r="N49" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/31）</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>完全遮光・形状記憶・晴雨兼用・UV日傘</t>
         </is>
       </c>
-      <c r="B49" s="35" t="n">
+      <c r="B50" s="35" t="n">
         <v>16.7</v>
       </c>
-      <c r="C49" s="10" t="n">
+      <c r="C50" s="10" t="n">
         <v>146281</v>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="D50" s="16" t="n">
         <v>2.12</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="E50" s="16" t="n">
         <v>2.64</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="F50" s="16" t="n">
         <v>1.37</v>
       </c>
-      <c r="G49" s="16" t="n">
+      <c r="G50" s="16" t="n">
         <v>0.75</v>
       </c>
-      <c r="H49" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="16" t="n">
+      <c r="H50" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="J49" s="8" t="inlineStr">
+      <c r="J50" s="8" t="inlineStr">
         <is>
           <t>7/31</t>
         </is>
       </c>
-      <c r="K49" s="10" t="n">
+      <c r="K50" s="10" t="n">
         <v>34000</v>
       </c>
-      <c r="L49" s="10" t="n">
+      <c r="L50" s="10" t="n">
         <v>34000</v>
       </c>
-      <c r="M49" s="8" t="inlineStr">
+      <c r="M50" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/31）</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="20" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>5WAY腰掛けファン</t>
         </is>
       </c>
-      <c r="B50" s="37" t="n">
+      <c r="B51" s="37" t="n">
         <v>11.3</v>
       </c>
-      <c r="C50" s="21" t="n">
+      <c r="C51" s="21" t="n">
         <v>127512</v>
       </c>
-      <c r="D50" s="23" t="n">
+      <c r="D51" s="23" t="n">
         <v>3.89</v>
       </c>
-      <c r="E50" s="23" t="n">
+      <c r="E51" s="23" t="n">
         <v>3.94</v>
       </c>
-      <c r="F50" s="23" t="n">
+      <c r="F51" s="23" t="n">
         <v>1.66</v>
       </c>
-      <c r="G50" s="23" t="n">
+      <c r="G51" s="23" t="n">
         <v>2.23</v>
       </c>
-      <c r="H50" s="38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="23" t="n">
+      <c r="H51" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="23" t="n">
         <v>9.25</v>
       </c>
-      <c r="J50" s="20" t="inlineStr">
+      <c r="J51" s="20" t="inlineStr">
         <is>
           <t>7/31</t>
         </is>
       </c>
-      <c r="K50" s="21" t="n">
+      <c r="K51" s="21" t="n">
         <v>16250</v>
       </c>
-      <c r="L50" s="21" t="n">
+      <c r="L51" s="21" t="n">
         <v>16250</v>
       </c>
-      <c r="M50" s="20" t="inlineStr">
+      <c r="M51" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N50" s="24" t="inlineStr">
+      <c r="N51" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 7/31）</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>ムダ毛シェーバー</t>
         </is>
       </c>
-      <c r="B51" s="35" t="n">
+      <c r="B52" s="35" t="n">
         <v>6.7</v>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C52" s="10" t="n">
         <v>82566</v>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D52" s="16" t="n">
         <v>3.44</v>
       </c>
-      <c r="E51" s="16" t="n">
+      <c r="E52" s="16" t="n">
         <v>4.67</v>
       </c>
-      <c r="F51" s="16" t="n">
+      <c r="F52" s="16" t="n">
         <v>1.77</v>
       </c>
-      <c r="G51" s="16" t="n">
+      <c r="G52" s="16" t="n">
         <v>1.67</v>
       </c>
-      <c r="H51" s="36" t="n">
+      <c r="H52" s="36" t="n">
         <v>0.911</v>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J51" s="8" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>8/3</t>
         </is>
       </c>
-      <c r="K51" s="10" t="n">
+      <c r="K52" s="10" t="n">
         <v>13000</v>
       </c>
-      <c r="L51" s="10" t="n">
+      <c r="L52" s="10" t="n">
         <v>13000</v>
       </c>
-      <c r="M51" s="8" t="inlineStr">
+      <c r="M52" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 8/3）</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="20" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
         <is>
           <t>瞬間冷感ポンチョ</t>
         </is>
       </c>
-      <c r="B52" s="37" t="n">
+      <c r="B53" s="37" t="n">
         <v>10.1</v>
       </c>
-      <c r="C52" s="21" t="n">
+      <c r="C53" s="21" t="n">
         <v>102762</v>
       </c>
-      <c r="D52" s="23" t="n">
+      <c r="D53" s="23" t="n">
         <v>2.91</v>
       </c>
-      <c r="E52" s="23" t="n">
+      <c r="E53" s="23" t="n">
         <v>2.6</v>
       </c>
-      <c r="F52" s="23" t="n">
+      <c r="F53" s="23" t="n">
         <v>1.36</v>
       </c>
-      <c r="G52" s="23" t="n">
+      <c r="G53" s="23" t="n">
         <v>1.55</v>
       </c>
-      <c r="H52" s="38" t="n">
+      <c r="H53" s="38" t="n">
         <v>1.049</v>
       </c>
-      <c r="I52" s="20" t="inlineStr">
+      <c r="I53" s="20" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J52" s="20" t="inlineStr">
+      <c r="J53" s="20" t="inlineStr">
         <is>
           <t>8/1</t>
         </is>
       </c>
-      <c r="K52" s="21" t="n">
+      <c r="K53" s="21" t="n">
         <v>13000</v>
       </c>
-      <c r="L52" s="21" t="n">
+      <c r="L53" s="21" t="n">
         <v>13000</v>
       </c>
-      <c r="M52" s="20" t="inlineStr">
+      <c r="M53" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N52" s="24" t="inlineStr">
+      <c r="N53" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 8/1）</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>偏光・調光サングラス</t>
         </is>
       </c>
-      <c r="B53" s="35" t="n">
+      <c r="B54" s="35" t="n">
         <v>9.4</v>
       </c>
-      <c r="C53" s="10" t="n">
+      <c r="C54" s="10" t="n">
         <v>46664</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="D54" s="16" t="n">
         <v>1.7</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="E54" s="16" t="n">
         <v>2.38</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="F54" s="16" t="n">
         <v>1.3</v>
       </c>
-      <c r="G53" s="16" t="n">
+      <c r="G54" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="H53" s="36" t="n">
+      <c r="H54" s="36" t="n">
         <v>0.981</v>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J53" s="8" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>8/5</t>
         </is>
       </c>
-      <c r="K53" s="10" t="n">
+      <c r="K54" s="10" t="n">
         <v>22000</v>
       </c>
-      <c r="L53" s="10" t="n">
+      <c r="L54" s="10" t="n">
         <v>22000</v>
       </c>
-      <c r="M53" s="8" t="inlineStr">
+      <c r="M54" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 8/5）</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
         <is>
           <t>接触冷感UVアームカバー</t>
         </is>
       </c>
-      <c r="B54" s="37" t="n">
+      <c r="B55" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="C54" s="21" t="n">
+      <c r="C55" s="21" t="n">
         <v>70858</v>
       </c>
-      <c r="D54" s="23" t="n">
+      <c r="D55" s="23" t="n">
         <v>1.96</v>
       </c>
-      <c r="E54" s="23" t="n">
+      <c r="E55" s="23" t="n">
         <v>2.23</v>
       </c>
-      <c r="F54" s="23" t="n">
+      <c r="F55" s="23" t="n">
         <v>1.25</v>
       </c>
-      <c r="G54" s="23" t="n">
+      <c r="G55" s="23" t="n">
         <v>0.71</v>
       </c>
-      <c r="H54" s="38" t="n">
+      <c r="H55" s="38" t="n">
         <v>1.176</v>
       </c>
-      <c r="I54" s="20" t="inlineStr">
+      <c r="I55" s="20" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J54" s="20" t="inlineStr">
+      <c r="J55" s="20" t="inlineStr">
         <is>
           <t>8/5</t>
         </is>
       </c>
-      <c r="K54" s="21" t="n">
+      <c r="K55" s="21" t="n">
         <v>17000</v>
       </c>
-      <c r="L54" s="21" t="n">
+      <c r="L55" s="21" t="n">
         <v>17000</v>
       </c>
-      <c r="M54" s="20" t="inlineStr">
+      <c r="M55" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N54" s="24" t="inlineStr">
+      <c r="N55" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 8/5）</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>3WAYサーキュレーター扇風機</t>
         </is>
       </c>
-      <c r="B55" s="35" t="n">
+      <c r="B56" s="35" t="n">
         <v>5.9</v>
       </c>
-      <c r="C55" s="10" t="n">
+      <c r="C56" s="10" t="n">
         <v>24719</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="D56" s="16" t="n">
         <v>2.16</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="E56" s="16" t="n">
         <v>4.6</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="F56" s="16" t="n">
         <v>1.76</v>
       </c>
-      <c r="G55" s="16" t="n">
+      <c r="G56" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="H55" s="36" t="n">
+      <c r="H56" s="36" t="n">
         <v>0.944</v>
       </c>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J55" s="8" t="inlineStr">
+      <c r="J56" s="8" t="inlineStr">
         <is>
           <t>なし(据置確定)</t>
         </is>
       </c>
-      <c r="K55" s="10" t="n">
+      <c r="K56" s="10" t="n">
         <v>16000</v>
       </c>
-      <c r="L55" s="10" t="n">
+      <c r="L56" s="10" t="n">
         <v>16000</v>
       </c>
-      <c r="M55" s="8" t="inlineStr">
+      <c r="M56" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="N56" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 なし(据置確定)）</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="20" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
         <is>
           <t>UV歯ブラシ除菌器</t>
         </is>
       </c>
-      <c r="B56" s="37" t="n">
+      <c r="B57" s="37" t="n">
         <v>2.7</v>
       </c>
-      <c r="C56" s="21" t="n">
+      <c r="C57" s="21" t="n">
         <v>37055</v>
       </c>
-      <c r="D56" s="23" t="n">
+      <c r="D57" s="23" t="n">
         <v>2.44</v>
       </c>
-      <c r="E56" s="23" t="n">
+      <c r="E57" s="23" t="n">
         <v>3.55</v>
       </c>
-      <c r="F56" s="23" t="n">
+      <c r="F57" s="23" t="n">
         <v>1.58</v>
       </c>
-      <c r="G56" s="23" t="n">
+      <c r="G57" s="23" t="n">
         <v>0.86</v>
       </c>
-      <c r="H56" s="38" t="n">
+      <c r="H57" s="38" t="n">
         <v>0.947</v>
       </c>
-      <c r="I56" s="20" t="inlineStr">
+      <c r="I57" s="20" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J56" s="20" t="inlineStr">
+      <c r="J57" s="20" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="K56" s="21" t="n">
+      <c r="K57" s="21" t="n">
         <v>10000</v>
       </c>
-      <c r="L56" s="21" t="n">
+      <c r="L57" s="21" t="n">
         <v>10000</v>
       </c>
-      <c r="M56" s="20" t="inlineStr">
+      <c r="M57" s="20" t="inlineStr">
         <is>
           <t>✅ 維持（判定合格）</t>
         </is>
       </c>
-      <c r="N56" s="24" t="inlineStr">
-        <is>
-          <t>S-1:本日が判定日 → S0:日販2.7個（&lt;10 利益率は参考値扱い） → S1:7日利益+37,055円→黒字 → S2:MER 2.44 &lt; 目標 3.55 → S2a:余裕+0.86&gt;0 → S2b:転用先の増分MERが実測で目標超えなのは5WAY腰掛けファンのみ。ただし判定日が7/31のため本日は転用しない→維持</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
+      <c r="N57" s="24" t="inlineStr">
+        <is>
+          <t>P-1:全店の週次MERが単週で−8%以上（-11.9%）→未測定のままの増額を禁止（増分MERが目標超えの増額のみ許可） → S-1:本日が判定日 → S0:日販2.7個（&lt;10 利益率は参考値扱い） → S1:7日利益+37,055円→黒字 → S2:MER 2.44 &lt; 目標 3.55 → S2a:余裕+0.86&gt;0 → S2b:転用先の増分MERが実測で目標超えなのは5WAY腰掛けファンのみ。ただし判定日が7/31のため本日は転用しない→維持</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>健康サンダル</t>
         </is>
       </c>
-      <c r="B57" s="35" t="n">
+      <c r="B58" s="35" t="n">
         <v>4.7</v>
       </c>
-      <c r="C57" s="10" t="n">
+      <c r="C58" s="10" t="n">
         <v>26720</v>
       </c>
-      <c r="D57" s="16" t="n">
+      <c r="D58" s="16" t="n">
         <v>1.71</v>
       </c>
-      <c r="E57" s="16" t="n">
+      <c r="E58" s="16" t="n">
         <v>2.47</v>
       </c>
-      <c r="F57" s="16" t="n">
+      <c r="F58" s="16" t="n">
         <v>1.32</v>
       </c>
-      <c r="G57" s="16" t="n">
+      <c r="G58" s="16" t="n">
         <v>0.39</v>
       </c>
-      <c r="H57" s="36" t="n">
+      <c r="H58" s="36" t="n">
         <v>0.955</v>
       </c>
-      <c r="I57" s="8" t="inlineStr">
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J57" s="8" t="inlineStr">
+      <c r="J58" s="8" t="inlineStr">
         <is>
           <t>なし(健全)</t>
         </is>
       </c>
-      <c r="K57" s="10" t="n">
+      <c r="K58" s="10" t="n">
         <v>13000</v>
       </c>
-      <c r="L57" s="10" t="n">
+      <c r="L58" s="10" t="n">
         <v>13000</v>
       </c>
-      <c r="M57" s="8" t="inlineStr">
+      <c r="M58" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 なし(健全)）</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="20" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="20" t="inlineStr">
         <is>
           <t>携帯電動シェーバー</t>
         </is>
       </c>
-      <c r="B58" s="37" t="n">
+      <c r="B59" s="37" t="n">
         <v>3.9</v>
       </c>
-      <c r="C58" s="21" t="n">
+      <c r="C59" s="21" t="n">
         <v>8796</v>
       </c>
-      <c r="D58" s="23" t="n">
+      <c r="D59" s="23" t="n">
         <v>1.71</v>
       </c>
-      <c r="E58" s="23" t="n">
+      <c r="E59" s="23" t="n">
         <v>3.33</v>
       </c>
-      <c r="F58" s="23" t="n">
+      <c r="F59" s="23" t="n">
         <v>1.54</v>
       </c>
-      <c r="G58" s="23" t="n">
+      <c r="G59" s="23" t="n">
         <v>0.17</v>
       </c>
-      <c r="H58" s="38" t="n">
+      <c r="H59" s="38" t="n">
         <v>1.094</v>
       </c>
-      <c r="I58" s="20" t="inlineStr">
+      <c r="I59" s="20" t="inlineStr">
         <is>
           <t>未測定/保留</t>
         </is>
       </c>
-      <c r="J58" s="20" t="inlineStr">
+      <c r="J59" s="20" t="inlineStr">
         <is>
           <t>8/5</t>
         </is>
       </c>
-      <c r="K58" s="21" t="n">
+      <c r="K59" s="21" t="n">
         <v>11000</v>
       </c>
-      <c r="L58" s="21" t="n">
+      <c r="L59" s="21" t="n">
         <v>11000</v>
       </c>
-      <c r="M58" s="20" t="inlineStr">
+      <c r="M59" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N58" s="24" t="inlineStr">
+      <c r="N59" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 8/5）</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>壁掛けディスペンサー</t>
         </is>
       </c>
-      <c r="B59" s="35" t="n">
+      <c r="B60" s="35" t="n">
         <v>1.7</v>
       </c>
-      <c r="C59" s="10" t="n">
+      <c r="C60" s="10" t="n">
         <v>-9961</v>
       </c>
-      <c r="D59" s="16" t="n">
+      <c r="D60" s="16" t="n">
         <v>1.29</v>
       </c>
-      <c r="E59" s="16" t="n">
+      <c r="E60" s="16" t="n">
         <v>3.44</v>
       </c>
-      <c r="F59" s="16" t="n">
+      <c r="F60" s="16" t="n">
         <v>1.56</v>
       </c>
-      <c r="G59" s="16" t="n">
+      <c r="G60" s="16" t="n">
         <v>-0.27</v>
       </c>
-      <c r="H59" s="36" t="n">
+      <c r="H60" s="36" t="n">
         <v>0.926</v>
       </c>
-      <c r="I59" s="16" t="n">
+      <c r="I60" s="16" t="n">
         <v>-0.1</v>
       </c>
-      <c r="J59" s="8" t="inlineStr">
+      <c r="J60" s="8" t="inlineStr">
         <is>
           <t>8/4</t>
         </is>
       </c>
-      <c r="K59" s="10" t="n">
+      <c r="K60" s="10" t="n">
         <v>6000</v>
       </c>
-      <c r="L59" s="10" t="n">
+      <c r="L60" s="10" t="n">
         <v>6000</v>
       </c>
-      <c r="M59" s="8" t="inlineStr">
+      <c r="M60" s="8" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="N60" s="5" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 8/4）</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="20" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="20" t="inlineStr">
         <is>
           <t>バランスケアスリッパ</t>
         </is>
       </c>
-      <c r="B60" s="37" t="n">
+      <c r="B61" s="37" t="n">
         <v>1.9</v>
       </c>
-      <c r="C60" s="21" t="n">
+      <c r="C61" s="21" t="n">
         <v>11172</v>
       </c>
-      <c r="D60" s="23" t="n">
+      <c r="D61" s="23" t="n">
         <v>1.81</v>
       </c>
-      <c r="E60" s="23" t="n">
+      <c r="E61" s="23" t="n">
         <v>2.63</v>
       </c>
-      <c r="F60" s="23" t="n">
+      <c r="F61" s="23" t="n">
         <v>1.37</v>
       </c>
-      <c r="G60" s="23" t="n">
+      <c r="G61" s="23" t="n">
         <v>0.44</v>
       </c>
-      <c r="H60" s="38" t="n">
+      <c r="H61" s="38" t="n">
         <v>0.931</v>
       </c>
-      <c r="I60" s="23" t="n">
+      <c r="I61" s="23" t="n">
         <v>1.89</v>
       </c>
-      <c r="J60" s="20" t="inlineStr">
+      <c r="J61" s="20" t="inlineStr">
         <is>
           <t>なし(健全)</t>
         </is>
       </c>
-      <c r="K60" s="21" t="n">
+      <c r="K61" s="21" t="n">
         <v>5000</v>
       </c>
-      <c r="L60" s="21" t="n">
+      <c r="L61" s="21" t="n">
         <v>5000</v>
       </c>
-      <c r="M60" s="20" t="inlineStr">
+      <c r="M61" s="20" t="inlineStr">
         <is>
           <t>👀 据置（監視のみ）</t>
         </is>
       </c>
-      <c r="N60" s="24" t="inlineStr">
+      <c r="N61" s="24" t="inlineStr">
         <is>
           <t>S-1:本日は判定日ではない（次回 なし(健全)）</t>
         </is>
